--- a/artfynd/A 62768-2021 artfynd.xlsx
+++ b/artfynd/A 62768-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62768-2021 artfynd.xlsx
+++ b/artfynd/A 62768-2021 artfynd.xlsx
@@ -675,58 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98450549</v>
+        <v>98450545</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Usansbo, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598469.4341088429</v>
+        <v>598388</v>
       </c>
       <c r="R2" t="n">
-        <v>6641618.619314938</v>
+        <v>6641893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,28 +743,17 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,12 +762,19 @@
           <t>Äldre barrblandskog</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>0</v>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0 substratenheter</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,41 +792,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98450547</v>
+        <v>98450541</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -857,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598405.6976759598</v>
+        <v>598438</v>
       </c>
       <c r="R3" t="n">
-        <v>6641765.500168663</v>
+        <v>6641899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +876,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,50 +919,61 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98450545</v>
+        <v>98450543</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Usansbo, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598388.2182903964</v>
+        <v>598468</v>
       </c>
       <c r="R4" t="n">
-        <v>6641893.528161091</v>
+        <v>6641855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,27 +1003,18 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,19 +1023,12 @@
           <t>Äldre barrblandskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>0</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>0 substratenheter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1075,15 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98450541</v>
+        <v>98450546</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598438.3527062623</v>
+        <v>598392</v>
       </c>
       <c r="R5" t="n">
-        <v>6641898.875804544</v>
+        <v>6641795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,19 +1130,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,12 +1176,7 @@
         <v>98450548</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598331.8843173054</v>
+        <v>598332</v>
       </c>
       <c r="R6" t="n">
-        <v>6641742.960289207</v>
+        <v>6641743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1306,19 +1257,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,49 +1300,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98450543</v>
+        <v>98450547</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1415,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598468.6660966956</v>
+        <v>598406</v>
       </c>
       <c r="R7" t="n">
-        <v>6641855.512963488</v>
+        <v>6641766</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1448,19 +1376,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1501,49 +1419,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98450546</v>
+        <v>98450549</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1557,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598391.3192312239</v>
+        <v>598470</v>
       </c>
       <c r="R8" t="n">
-        <v>6641795.735871104</v>
+        <v>6641618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1590,19 +1495,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 62768-2021 artfynd.xlsx
+++ b/artfynd/A 62768-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450545</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450541</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450543</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,6 +1190,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450546</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1416,6 +1446,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450547</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1535,8 +1570,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450549</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>